--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>80</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.53e+05</t>
-  </si>
-  <si>
-    <t>(67025.175)</t>
-  </si>
-  <si>
-    <t>489.848</t>
-  </si>
-  <si>
-    <t>(33.620)</t>
-  </si>
-  <si>
-    <t>3.587</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>10.914</t>
-  </si>
-  <si>
-    <t>(1.815)</t>
-  </si>
-  <si>
-    <t>88.599</t>
-  </si>
-  <si>
-    <t>(0.469)</t>
-  </si>
-  <si>
-    <t>1.07e+06</t>
-  </si>
-  <si>
-    <t>(54625.452)</t>
-  </si>
-  <si>
-    <t>2.535</t>
-  </si>
-  <si>
-    <t>(0.125)</t>
-  </si>
-  <si>
-    <t>3.383</t>
-  </si>
-  <si>
-    <t>(0.435)</t>
-  </si>
-  <si>
-    <t>33.444</t>
-  </si>
-  <si>
-    <t>(3.417)</t>
-  </si>
-  <si>
-    <t>0.951</t>
-  </si>
-  <si>
-    <t>(0.024)</t>
-  </si>
-  <si>
-    <t>35</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.55e+05</t>
-  </si>
-  <si>
-    <t>(1.50e+05)</t>
-  </si>
-  <si>
-    <t>499.086</t>
-  </si>
-  <si>
-    <t>(58.051)</t>
-  </si>
-  <si>
-    <t>3.358</t>
-  </si>
-  <si>
-    <t>(0.063)</t>
-  </si>
-  <si>
-    <t>27.857</t>
-  </si>
-  <si>
-    <t>(4.415)</t>
-  </si>
-  <si>
-    <t>91.038</t>
-  </si>
-  <si>
-    <t>(0.501)</t>
-  </si>
-  <si>
-    <t>1.32e+06</t>
-  </si>
-  <si>
-    <t>(76899.243)</t>
-  </si>
-  <si>
-    <t>3.348</t>
-  </si>
-  <si>
-    <t>(0.160)</t>
-  </si>
-  <si>
-    <t>6.314</t>
-  </si>
-  <si>
-    <t>(0.659)</t>
-  </si>
-  <si>
-    <t>45.229</t>
-  </si>
-  <si>
-    <t>(3.670)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>2.02e+05</t>
-  </si>
-  <si>
-    <t>9.238</t>
-  </si>
-  <si>
-    <t>-0.230***</t>
-  </si>
-  <si>
-    <t>16.944***</t>
-  </si>
-  <si>
-    <t>2.439***</t>
-  </si>
-  <si>
-    <t>2.52e+05**</t>
-  </si>
-  <si>
-    <t>0.813***</t>
-  </si>
-  <si>
-    <t>2.932***</t>
-  </si>
-  <si>
-    <t>11.784**</t>
-  </si>
-  <si>
-    <t>0.049</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>81</t>
+  </si>
+  <si>
+    <t>80</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.53e+05</t>
+  </si>
+  <si>
+    <t>(67025.175)</t>
+  </si>
+  <si>
+    <t>489.848</t>
+  </si>
+  <si>
+    <t>(33.620)</t>
+  </si>
+  <si>
+    <t>3.587</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>10.914</t>
+  </si>
+  <si>
+    <t>(1.815)</t>
+  </si>
+  <si>
+    <t>88.599</t>
+  </si>
+  <si>
+    <t>(0.469)</t>
+  </si>
+  <si>
+    <t>1.07e+06</t>
+  </si>
+  <si>
+    <t>(54625.452)</t>
+  </si>
+  <si>
+    <t>2.535</t>
+  </si>
+  <si>
+    <t>(0.125)</t>
+  </si>
+  <si>
+    <t>3.383</t>
+  </si>
+  <si>
+    <t>(0.435)</t>
+  </si>
+  <si>
+    <t>33.444</t>
+  </si>
+  <si>
+    <t>(3.417)</t>
+  </si>
+  <si>
+    <t>0.951</t>
+  </si>
+  <si>
+    <t>(0.024)</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.55e+05</t>
+  </si>
+  <si>
+    <t>(1.50e+05)</t>
+  </si>
+  <si>
+    <t>499.086</t>
+  </si>
+  <si>
+    <t>(58.051)</t>
+  </si>
+  <si>
+    <t>3.358</t>
+  </si>
+  <si>
+    <t>(0.063)</t>
+  </si>
+  <si>
+    <t>27.857</t>
+  </si>
+  <si>
+    <t>(4.415)</t>
+  </si>
+  <si>
+    <t>91.038</t>
+  </si>
+  <si>
+    <t>(0.501)</t>
+  </si>
+  <si>
+    <t>1.32e+06</t>
+  </si>
+  <si>
+    <t>(76899.243)</t>
+  </si>
+  <si>
+    <t>3.348</t>
+  </si>
+  <si>
+    <t>(0.160)</t>
+  </si>
+  <si>
+    <t>6.314</t>
+  </si>
+  <si>
+    <t>(0.659)</t>
+  </si>
+  <si>
+    <t>45.229</t>
+  </si>
+  <si>
+    <t>(3.670)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>2.02e+05</t>
+  </si>
+  <si>
+    <t>9.238</t>
+  </si>
+  <si>
+    <t>-0.230***</t>
+  </si>
+  <si>
+    <t>16.944***</t>
+  </si>
+  <si>
+    <t>2.439***</t>
+  </si>
+  <si>
+    <t>2.52e+05**</t>
+  </si>
+  <si>
+    <t>0.813***</t>
+  </si>
+  <si>
+    <t>2.932***</t>
+  </si>
+  <si>
+    <t>11.784**</t>
+  </si>
+  <si>
+    <t>0.049</t>
   </si>
 </sst>
 </file>
